--- a/data/Arisdorf/cost/cost_report.xlsx
+++ b/data/Arisdorf/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337.8384526004675</v>
+        <v>346.7456829274402</v>
       </c>
       <c r="C2" t="n">
-        <v>5945.647080950263</v>
+        <v>4974.330783896216</v>
       </c>
       <c r="D2" t="n">
-        <v>11462.66329692092</v>
+        <v>19769.42673337548</v>
       </c>
       <c r="E2" t="n">
-        <v>1275.025676759714</v>
+        <v>1498.798702574818</v>
       </c>
       <c r="F2" t="n">
-        <v>11925.86722305355</v>
+        <v>11103.15637566546</v>
       </c>
       <c r="G2" t="n">
-        <v>30947.04173028492</v>
+        <v>37692.45827843942</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1065302165576035</v>
+        <v>0.1297032231899268</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>337.8386706937442</v>
+        <v>345.8942422480428</v>
       </c>
       <c r="C3" t="n">
-        <v>5823.51348064833</v>
+        <v>7773.126857155303</v>
       </c>
       <c r="D3" t="n">
-        <v>11777.4321694145</v>
+        <v>1630.570502720921</v>
       </c>
       <c r="E3" t="n">
-        <v>1296.079795066625</v>
+        <v>1548.762610412773</v>
       </c>
       <c r="F3" t="n">
-        <v>12276.91658391796</v>
+        <v>17712.86253687297</v>
       </c>
       <c r="G3" t="n">
-        <v>31511.78069974116</v>
+        <v>29011.21674941001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1084742396806866</v>
+        <v>0.09983027090627486</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>337.8590537281266</v>
+        <v>346.0072769605338</v>
       </c>
       <c r="C4" t="n">
-        <v>5282.483521803108</v>
+        <v>7645.899644303953</v>
       </c>
       <c r="D4" t="n">
-        <v>14081.46441075925</v>
+        <v>1718.512237363475</v>
       </c>
       <c r="E4" t="n">
-        <v>1270.705291458977</v>
+        <v>1610.64313008558</v>
       </c>
       <c r="F4" t="n">
-        <v>10278.11970093072</v>
+        <v>18268.94489044246</v>
       </c>
       <c r="G4" t="n">
-        <v>31250.63197868018</v>
+        <v>29590.007179156</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1075752771869261</v>
+        <v>0.1018219421242935</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>337.8590537281266</v>
+        <v>346.6818329806387</v>
       </c>
       <c r="C5" t="n">
-        <v>5158.296746892899</v>
+        <v>5081.069144809421</v>
       </c>
       <c r="D5" t="n">
-        <v>14394.2157663444</v>
+        <v>19779.55209089349</v>
       </c>
       <c r="E5" t="n">
-        <v>1293.929384229356</v>
+        <v>1432.699461483062</v>
       </c>
       <c r="F5" t="n">
-        <v>10630.96283437528</v>
+        <v>10469.82214174605</v>
       </c>
       <c r="G5" t="n">
-        <v>31815.26378557006</v>
+        <v>37109.82467191266</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1095189314201004</v>
+        <v>0.1276983272463656</v>
       </c>
     </row>
   </sheetData>

--- a/data/Arisdorf/cost/cost_report.xlsx
+++ b/data/Arisdorf/cost/cost_report.xlsx
@@ -482,30 +482,30 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>346.7456829274402</v>
+        <v>288.2857042088274</v>
       </c>
       <c r="C2" t="n">
-        <v>4974.330783896216</v>
+        <v>7648.591636288949</v>
       </c>
       <c r="D2" t="n">
-        <v>19769.42673337548</v>
+        <v>3532.176009822292</v>
       </c>
       <c r="E2" t="n">
-        <v>1498.798702574818</v>
+        <v>1583.106810214322</v>
       </c>
       <c r="F2" t="n">
-        <v>11103.15637566546</v>
+        <v>16838.09281846349</v>
       </c>
       <c r="G2" t="n">
-        <v>37692.45827843942</v>
+        <v>29890.25297899789</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>base</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1297032231899268</v>
+        <v>0.1028551155963195</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>345.8942422480428</v>
+        <v>287.4173471566997</v>
       </c>
       <c r="C3" t="n">
-        <v>7773.126857155303</v>
+        <v>7550.591984597716</v>
       </c>
       <c r="D3" t="n">
-        <v>1630.570502720921</v>
+        <v>4084.09233618608</v>
       </c>
       <c r="E3" t="n">
-        <v>1548.762610412773</v>
+        <v>1164.991320259659</v>
       </c>
       <c r="F3" t="n">
-        <v>17712.86253687297</v>
+        <v>17377.12249509925</v>
       </c>
       <c r="G3" t="n">
-        <v>29011.21674941001</v>
+        <v>30464.21548329941</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.09983027090627486</v>
+        <v>0.104830173477876</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>346.0072769605338</v>
+        <v>283.8815540025115</v>
       </c>
       <c r="C4" t="n">
-        <v>7645.899644303953</v>
+        <v>5039.481023928129</v>
       </c>
       <c r="D4" t="n">
-        <v>1718.512237363475</v>
+        <v>21736.91297379015</v>
       </c>
       <c r="E4" t="n">
-        <v>1610.64313008558</v>
+        <v>960.0525567986597</v>
       </c>
       <c r="F4" t="n">
-        <v>18268.94489044246</v>
+        <v>9603.500293504298</v>
       </c>
       <c r="G4" t="n">
-        <v>29590.007179156</v>
+        <v>37623.82840202374</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1018219421242935</v>
+        <v>0.1294670614593099</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>346.6818329806387</v>
+        <v>283.2981536830889</v>
       </c>
       <c r="C5" t="n">
-        <v>5081.069144809421</v>
+        <v>4958.340535321063</v>
       </c>
       <c r="D5" t="n">
-        <v>19779.55209089349</v>
+        <v>21673.38876366966</v>
       </c>
       <c r="E5" t="n">
-        <v>1432.699461483062</v>
+        <v>1039.428333881749</v>
       </c>
       <c r="F5" t="n">
-        <v>10469.82214174605</v>
+        <v>10232.83736879853</v>
       </c>
       <c r="G5" t="n">
-        <v>37109.82467191266</v>
+        <v>38187.2931553541</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1276983272463656</v>
+        <v>0.1314059956121579</v>
       </c>
     </row>
   </sheetData>
